--- a/ONLINE2.xlsx
+++ b/ONLINE2.xlsx
@@ -10,7 +10,7 @@
     <sheet name="HTC" sheetId="2" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">HTC!$A$1:$E$23</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">HTC!$A$1:$F$23</definedName>
   </definedNames>
   <calcPr calcId="191029" iterate="1" iterateCount="100" iterateDelta="0.001"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="41">
   <si>
     <t>S.NO</t>
   </si>
@@ -38,6 +38,9 @@
     <t>AUDIT DIVISION</t>
   </si>
   <si>
+    <t>GROUP</t>
+  </si>
+  <si>
     <t>DEPARTMENT</t>
   </si>
   <si>
@@ -50,6 +53,9 @@
     <t>HAD</t>
   </si>
   <si>
+    <t>GROUP-A</t>
+  </si>
+  <si>
     <t>PAYROLL</t>
   </si>
   <si>
@@ -86,6 +92,9 @@
     <t>CHEQUE COLLECTION RECONCILIATION</t>
   </si>
   <si>
+    <t>GROUP-B</t>
+  </si>
+  <si>
     <t>DIAGNOSTICS COMMERCIAL</t>
   </si>
   <si>
@@ -141,6 +150,9 @@
   </si>
   <si>
     <t>CLINICS</t>
+  </si>
+  <si>
+    <t>GROUP-C</t>
   </si>
 </sst>
 </file>
@@ -778,7 +790,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="6" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="6"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="6" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1098,17 +1110,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E23"/>
-  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelCol="4"/>
+  <dimension ref="A1:F23"/>
+  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
-    <col min="2" max="2" width="16.4285714285714" customWidth="1"/>
-    <col min="3" max="3" width="44.5714285714286" customWidth="1"/>
-    <col min="4" max="4" width="43.4285714285714" customWidth="1"/>
-    <col min="5" max="5" width="25.5714285714286" customWidth="1"/>
+    <col min="2" max="3" width="16.4285714285714" customWidth="1"/>
+    <col min="4" max="4" width="44.5714285714286" customWidth="1"/>
+    <col min="5" max="5" width="43.4285714285714" customWidth="1"/>
+    <col min="6" max="6" width="40.5714285714286" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1118,328 +1130,397 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:5">
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
       <c r="A2" s="3">
         <f>ROW()-1</f>
         <v>1</v>
       </c>
       <c r="B2" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="3">
+        <f t="shared" ref="A3:A23" si="0">ROW()-1</f>
+        <v>2</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="3">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F4" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="3">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="3">
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="C2" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3" s="3">
-        <f t="shared" ref="A3:A12" si="0">ROW()-1</f>
-        <v>2</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" s="4" t="s">
+      <c r="B6" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D6" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="E6" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="3">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="3">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="3">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="3">
+        <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="B10" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="3">
+        <f t="shared" si="0"/>
         <v>10</v>
       </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4" s="3">
-        <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D4" s="7" t="s">
+      <c r="B11" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="3">
+        <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="E4" s="8" t="s">
+      <c r="B12" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="3">
+        <f t="shared" si="0"/>
         <v>12</v>
       </c>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5" s="3">
-        <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D5" s="5" t="s">
+      <c r="B13" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="3">
+        <f t="shared" si="0"/>
         <v>13</v>
       </c>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="A6" s="3">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D6" s="5" t="s">
+      <c r="B14" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="3">
+        <f t="shared" si="0"/>
         <v>14</v>
       </c>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="A7" s="3">
-        <f t="shared" si="0"/>
-        <v>6</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D7" s="5" t="s">
+      <c r="B15" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="3">
+        <f t="shared" si="0"/>
         <v>15</v>
       </c>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="A8" s="3">
-        <f t="shared" si="0"/>
-        <v>7</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D8" s="5" t="s">
+      <c r="B16" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
+      <c r="A17" s="3">
+        <f t="shared" si="0"/>
         <v>16</v>
       </c>
-    </row>
-    <row r="9" spans="1:5">
-      <c r="A9" s="3">
-        <f t="shared" si="0"/>
-        <v>8</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D9" s="5" t="s">
+      <c r="B17" t="s">
+        <v>31</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="F17" s="9" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
+      <c r="A18" s="3">
+        <f t="shared" si="0"/>
         <v>17</v>
       </c>
-    </row>
-    <row r="10" spans="1:5">
-      <c r="A10" s="3">
-        <f t="shared" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C10" s="4" t="s">
+      <c r="B18" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D18" s="3"/>
+    </row>
+    <row r="19" spans="1:6">
+      <c r="A19" s="3">
+        <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="D10" s="5" t="s">
+      <c r="B19" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D19" s="3"/>
+    </row>
+    <row r="20" spans="1:6">
+      <c r="A20" s="3">
+        <f t="shared" si="0"/>
         <v>19</v>
       </c>
-    </row>
-    <row r="11" spans="1:5">
-      <c r="A11" s="3">
-        <f t="shared" si="0"/>
-        <v>10</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="D11" s="5" t="s">
+      <c r="B20" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D20" s="3"/>
+    </row>
+    <row r="21" spans="1:6">
+      <c r="A21" s="3">
+        <f t="shared" si="0"/>
         <v>20</v>
       </c>
-    </row>
-    <row r="12" spans="1:5">
-      <c r="A12" s="3">
-        <f t="shared" si="0"/>
-        <v>11</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="D12" s="5" t="s">
+      <c r="B21" t="s">
+        <v>38</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6">
+      <c r="A22" s="3">
+        <f t="shared" si="0"/>
         <v>21</v>
       </c>
-    </row>
-    <row r="13" spans="1:5">
-      <c r="A13" s="3">
-        <f>ROW()-1</f>
-        <v>12</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C13" s="4" t="s">
+      <c r="B22" t="s">
+        <v>39</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6">
+      <c r="A23" s="3">
+        <f t="shared" si="0"/>
         <v>22</v>
       </c>
-      <c r="D13" s="5" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5">
-      <c r="A14" s="3">
-        <f>ROW()-1</f>
-        <v>13</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="D14" s="5" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5">
-      <c r="A15" s="3">
-        <f>ROW()-1</f>
-        <v>14</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="D15" s="5" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5">
-      <c r="A16" s="3">
-        <f>ROW()-1</f>
-        <v>15</v>
-      </c>
-      <c r="B16" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="D16" s="5" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="3">
-        <f>ROW()-1</f>
-        <v>16</v>
-      </c>
-      <c r="B17" t="s">
-        <v>28</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="D17" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="E17" s="9" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="3">
-        <f>ROW()-1</f>
-        <v>17</v>
-      </c>
-      <c r="B18" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="C18" s="3"/>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="3">
-        <f>ROW()-1</f>
-        <v>18</v>
-      </c>
-      <c r="B19" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C19" s="3"/>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="3">
-        <f>ROW()-1</f>
-        <v>19</v>
-      </c>
-      <c r="B20" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C20" s="3"/>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="3">
-        <f>ROW()-1</f>
-        <v>20</v>
-      </c>
-      <c r="B21" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="3">
-        <f>ROW()-1</f>
-        <v>21</v>
-      </c>
-      <c r="B22" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="3">
-        <f>ROW()-1</f>
-        <v>22</v>
-      </c>
       <c r="B23" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>40</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:E23" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:F23" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <hyperlinks>
-    <hyperlink ref="E3" r:id="rId1" display="http://192.168.0.110:8502"/>
-    <hyperlink ref="L4" r:id="rId2"/>
-    <hyperlink ref="E4" r:id="rId2" display="http://192.168.0.110:8503"/>
-    <hyperlink ref="E17" r:id="rId3" display="https://auditincentivecal.streamlit.app/"/>
+    <hyperlink ref="F3" r:id="rId1" display="http://192.168.0.110:8502"/>
+    <hyperlink ref="M4" r:id="rId2"/>
+    <hyperlink ref="F4" r:id="rId2" display="http://192.168.0.110:8503"/>
+    <hyperlink ref="F17" r:id="rId3" display="https://auditincentivecal.streamlit.app/"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/ONLINE2.xlsx
+++ b/ONLINE2.xlsx
@@ -10,7 +10,7 @@
     <sheet name="HTC" sheetId="2" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">HTC!$A$1:$F$23</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">HTC!$A$1:$E$23</definedName>
   </definedNames>
   <calcPr calcId="191029" iterate="1" iterateCount="100" iterateDelta="0.001"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="37">
   <si>
     <t>S.NO</t>
   </si>
@@ -38,9 +38,6 @@
     <t>AUDIT DIVISION</t>
   </si>
   <si>
-    <t>GROUP</t>
-  </si>
-  <si>
     <t>DEPARTMENT</t>
   </si>
   <si>
@@ -53,9 +50,6 @@
     <t>HAD</t>
   </si>
   <si>
-    <t>GROUP-A</t>
-  </si>
-  <si>
     <t>PAYROLL</t>
   </si>
   <si>
@@ -92,9 +86,6 @@
     <t>CHEQUE COLLECTION RECONCILIATION</t>
   </si>
   <si>
-    <t>GROUP-B</t>
-  </si>
-  <si>
     <t>DIAGNOSTICS COMMERCIAL</t>
   </si>
   <si>
@@ -150,9 +141,6 @@
   </si>
   <si>
     <t>CLINICS</t>
-  </si>
-  <si>
-    <t>GROUP-C</t>
   </si>
 </sst>
 </file>
@@ -790,7 +778,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="6" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="6" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="6"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1110,17 +1098,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F23"/>
-  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelCol="5"/>
+  <dimension ref="A1:E23"/>
+  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
-    <col min="2" max="3" width="16.4285714285714" customWidth="1"/>
-    <col min="4" max="4" width="44.5714285714286" customWidth="1"/>
-    <col min="5" max="5" width="43.4285714285714" customWidth="1"/>
-    <col min="6" max="6" width="40.5714285714286" customWidth="1"/>
+    <col min="2" max="2" width="16.4285714285714" customWidth="1"/>
+    <col min="3" max="3" width="44.5714285714286" customWidth="1"/>
+    <col min="4" max="4" width="43.4285714285714" customWidth="1"/>
+    <col min="5" max="5" width="25.5714285714286" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1130,397 +1118,328 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
+    </row>
+    <row r="2" spans="1:5">
       <c r="A2" s="3">
         <f>ROW()-1</f>
         <v>1</v>
       </c>
       <c r="B2" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="D2" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="4" t="s">
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="3">
+        <f t="shared" ref="A3:A12" si="0">ROW()-1</f>
+        <v>2</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="D3" s="5" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="3">
-        <f t="shared" ref="A3:A23" si="0">ROW()-1</f>
-        <v>2</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D3" s="4" t="s">
+      <c r="E3" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="E3" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F3" s="6" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
+    </row>
+    <row r="4" spans="1:5">
       <c r="A4" s="3">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="E4" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F4" s="8" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
+        <v>8</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
       <c r="A5" s="3">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="B5" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
+      <c r="D5" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
       <c r="A6" s="3">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="B6" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
+      <c r="D6" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
       <c r="A7" s="3">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
       <c r="B7" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C7" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
+      <c r="D7" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
       <c r="A8" s="3">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
+        <v>8</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
       <c r="A9" s="3">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
+        <v>8</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
       <c r="A10" s="3">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="E10" s="5" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
+        <v>18</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
       <c r="A11" s="3">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C11" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D11" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="D11" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="E11" s="5" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
+    </row>
+    <row r="12" spans="1:5">
       <c r="A12" s="3">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C12" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" s="3">
+        <f>ROW()-1</f>
+        <v>12</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" s="3">
+        <f>ROW()-1</f>
+        <v>13</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" s="3">
+        <f>ROW()-1</f>
+        <v>14</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" s="3">
+        <f>ROW()-1</f>
+        <v>15</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="3">
+        <f>ROW()-1</f>
+        <v>16</v>
+      </c>
+      <c r="B17" t="s">
+        <v>28</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="E17" s="9" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="3">
+        <f>ROW()-1</f>
+        <v>17</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C18" s="3"/>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="3">
+        <f>ROW()-1</f>
+        <v>18</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C19" s="3"/>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="3">
+        <f>ROW()-1</f>
+        <v>19</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C20" s="3"/>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="3">
+        <f>ROW()-1</f>
         <v>20</v>
       </c>
-      <c r="D12" s="4" t="s">
+      <c r="B21" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="3">
+        <f>ROW()-1</f>
         <v>21</v>
       </c>
-      <c r="E12" s="5" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="3">
-        <f t="shared" si="0"/>
-        <v>12</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="E13" s="5" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="3">
-        <f t="shared" si="0"/>
-        <v>13</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D14" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="E14" s="5" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="3">
-        <f t="shared" si="0"/>
-        <v>14</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D15" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="E15" s="5" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="3">
-        <f t="shared" si="0"/>
-        <v>15</v>
-      </c>
-      <c r="B16" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D16" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="E16" s="5" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17" s="3">
-        <f t="shared" si="0"/>
-        <v>16</v>
-      </c>
-      <c r="B17" t="s">
-        <v>31</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D17" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="E17" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="F17" s="9" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18" s="3">
-        <f t="shared" si="0"/>
-        <v>17</v>
-      </c>
-      <c r="B18" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D18" s="3"/>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="A19" s="3">
-        <f t="shared" si="0"/>
-        <v>18</v>
-      </c>
-      <c r="B19" s="4" t="s">
+      <c r="B22" t="s">
         <v>36</v>
       </c>
-      <c r="C19" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D19" s="3"/>
-    </row>
-    <row r="20" spans="1:6">
-      <c r="A20" s="3">
-        <f t="shared" si="0"/>
-        <v>19</v>
-      </c>
-      <c r="B20" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="C20" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D20" s="3"/>
-    </row>
-    <row r="21" spans="1:6">
-      <c r="A21" s="3">
-        <f t="shared" si="0"/>
-        <v>20</v>
-      </c>
-      <c r="B21" t="s">
-        <v>38</v>
-      </c>
-      <c r="C21" s="4" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
-      <c r="A22" s="3">
-        <f t="shared" si="0"/>
-        <v>21</v>
-      </c>
-      <c r="B22" t="s">
-        <v>39</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6">
+    </row>
+    <row r="23" spans="1:5">
       <c r="A23" s="3">
-        <f t="shared" si="0"/>
+        <f>ROW()-1</f>
         <v>22</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C23" s="4" t="s">
-        <v>40</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:F23" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:E23" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <hyperlinks>
-    <hyperlink ref="F3" r:id="rId1" display="http://192.168.0.110:8502"/>
-    <hyperlink ref="M4" r:id="rId2"/>
-    <hyperlink ref="F4" r:id="rId2" display="http://192.168.0.110:8503"/>
-    <hyperlink ref="F17" r:id="rId3" display="https://auditincentivecal.streamlit.app/"/>
+    <hyperlink ref="E3" r:id="rId1" display="http://192.168.0.110:8502"/>
+    <hyperlink ref="L4" r:id="rId2"/>
+    <hyperlink ref="E4" r:id="rId2" display="http://192.168.0.110:8503"/>
+    <hyperlink ref="E17" r:id="rId3" display="https://auditincentivecal.streamlit.app/"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/ONLINE2.xlsx
+++ b/ONLINE2.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="41">
   <si>
     <t>S.NO</t>
   </si>
@@ -141,6 +141,18 @@
   </si>
   <si>
     <t>CLINICS</t>
+  </si>
+  <si>
+    <t>ADMIN</t>
+  </si>
+  <si>
+    <t>ALL DEPARTMENTS</t>
+  </si>
+  <si>
+    <t>PDF TO EXCEL</t>
+  </si>
+  <si>
+    <t>PPT PREPARATION</t>
   </si>
 </sst>
 </file>
@@ -778,7 +790,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="6" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="6"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="6" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1098,7 +1110,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E23"/>
+  <dimension ref="A1:E24"/>
   <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -1142,7 +1154,7 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="3">
-        <f t="shared" ref="A3:A12" si="0">ROW()-1</f>
+        <f t="shared" ref="A3:A23" si="0">ROW()-1</f>
         <v>2</v>
       </c>
       <c r="B3" s="4" t="s">
@@ -1298,7 +1310,7 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="0"/>
         <v>12</v>
       </c>
       <c r="B13" s="4" t="s">
@@ -1313,7 +1325,7 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="0"/>
         <v>13</v>
       </c>
       <c r="B14" s="4" t="s">
@@ -1328,7 +1340,7 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="0"/>
         <v>14</v>
       </c>
       <c r="B15" s="4" t="s">
@@ -1343,7 +1355,7 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="0"/>
         <v>15</v>
       </c>
       <c r="B16" s="4" t="s">
@@ -1358,7 +1370,7 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="0"/>
         <v>16</v>
       </c>
       <c r="B17" t="s">
@@ -1376,7 +1388,7 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="0"/>
         <v>17</v>
       </c>
       <c r="B18" s="4" t="s">
@@ -1386,7 +1398,7 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="0"/>
         <v>18</v>
       </c>
       <c r="B19" s="4" t="s">
@@ -1396,7 +1408,7 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="0"/>
         <v>19</v>
       </c>
       <c r="B20" s="4" t="s">
@@ -1406,7 +1418,7 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="0"/>
         <v>20</v>
       </c>
       <c r="B21" t="s">
@@ -1415,7 +1427,7 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="0"/>
         <v>21</v>
       </c>
       <c r="B22" t="s">
@@ -1424,11 +1436,32 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="3">
+        <f t="shared" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C23" t="s">
+        <v>38</v>
+      </c>
+      <c r="D23" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="3">
         <f>ROW()-1</f>
-        <v>22</v>
-      </c>
-      <c r="B23" s="4" t="s">
-        <v>5</v>
+        <v>23</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C24" t="s">
+        <v>38</v>
+      </c>
+      <c r="D24" t="s">
+        <v>40</v>
       </c>
     </row>
   </sheetData>

--- a/ONLINE2.xlsx
+++ b/ONLINE2.xlsx
@@ -10,7 +10,7 @@
     <sheet name="HTC" sheetId="2" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">HTC!$A$1:$E$23</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">HTC!$A$1:$E$26</definedName>
   </definedNames>
   <calcPr calcId="191029" iterate="1" iterateCount="100" iterateDelta="0.001"/>
   <extLst>
@@ -116,6 +116,18 @@
     <t>CONSULTANTS PAY SHEET VERIFICATION</t>
   </si>
   <si>
+    <t>ADMIN</t>
+  </si>
+  <si>
+    <t>ALL DEPARTMENTS</t>
+  </si>
+  <si>
+    <t>PDF TO EXCEL</t>
+  </si>
+  <si>
+    <t>PPT PREPARATION</t>
+  </si>
+  <si>
     <t>CENTRAL</t>
   </si>
   <si>
@@ -141,18 +153,6 @@
   </si>
   <si>
     <t>CLINICS</t>
-  </si>
-  <si>
-    <t>ADMIN</t>
-  </si>
-  <si>
-    <t>ALL DEPARTMENTS</t>
-  </si>
-  <si>
-    <t>PDF TO EXCEL</t>
-  </si>
-  <si>
-    <t>PPT PREPARATION</t>
   </si>
 </sst>
 </file>
@@ -774,7 +774,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -789,7 +789,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="6" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="6" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="49">
@@ -1110,14 +1109,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E24"/>
+  <dimension ref="A1:E26"/>
   <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
     <col min="2" max="2" width="16.4285714285714" customWidth="1"/>
     <col min="3" max="3" width="44.5714285714286" customWidth="1"/>
     <col min="4" max="4" width="43.4285714285714" customWidth="1"/>
-    <col min="5" max="5" width="25.5714285714286" customWidth="1"/>
+    <col min="5" max="5" width="40.4285714285714" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -1154,7 +1153,7 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="3">
-        <f t="shared" ref="A3:A23" si="0">ROW()-1</f>
+        <f t="shared" ref="A3:A24" si="0">ROW()-1</f>
         <v>2</v>
       </c>
       <c r="B3" s="4" t="s">
@@ -1370,82 +1369,88 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="3">
-        <f t="shared" si="0"/>
+        <f>ROW()-1</f>
         <v>16</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B17" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C17" s="4" t="s">
+      <c r="C17" t="s">
         <v>29</v>
       </c>
-      <c r="D17" s="5" t="s">
+      <c r="D17" t="s">
         <v>30</v>
-      </c>
-      <c r="E17" s="9" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="3">
-        <f t="shared" si="0"/>
+        <f>ROW()-1</f>
         <v>17</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="C18" s="3"/>
+        <v>28</v>
+      </c>
+      <c r="C18" t="s">
+        <v>29</v>
+      </c>
+      <c r="D18" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="3">
-        <f t="shared" si="0"/>
+        <f>ROW()-1</f>
         <v>18</v>
       </c>
-      <c r="B19" s="4" t="s">
+      <c r="B19" t="s">
+        <v>32</v>
+      </c>
+      <c r="C19" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="C19" s="3"/>
+      <c r="D19" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E19" s="8" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="3">
-        <f t="shared" si="0"/>
+        <f>ROW()-1</f>
         <v>19</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C20" s="3"/>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="3">
-        <f t="shared" si="0"/>
+        <f>ROW()-1</f>
         <v>20</v>
       </c>
-      <c r="B21" t="s">
-        <v>35</v>
-      </c>
+      <c r="B21" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C21" s="3"/>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="3">
-        <f t="shared" si="0"/>
+        <f>ROW()-1</f>
         <v>21</v>
       </c>
-      <c r="B22" t="s">
-        <v>36</v>
-      </c>
+      <c r="B22" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="C22" s="3"/>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="3">
-        <f t="shared" si="0"/>
+        <f>ROW()-1</f>
         <v>22</v>
       </c>
-      <c r="B23" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="C23" t="s">
-        <v>38</v>
-      </c>
-      <c r="D23" t="s">
+      <c r="B23" t="s">
         <v>39</v>
       </c>
     </row>
@@ -1454,25 +1459,31 @@
         <f>ROW()-1</f>
         <v>23</v>
       </c>
-      <c r="B24" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="C24" t="s">
-        <v>38</v>
-      </c>
-      <c r="D24" t="s">
+      <c r="B24" t="s">
         <v>40</v>
       </c>
     </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="3">
+        <f>ROW()-1</f>
+        <v>24</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="3">
+        <f>ROW()-1</f>
+        <v>25</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:E23" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:E26" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <hyperlinks>
     <hyperlink ref="E3" r:id="rId1" display="http://192.168.0.110:8502"/>
     <hyperlink ref="L4" r:id="rId2"/>
     <hyperlink ref="E4" r:id="rId2" display="http://192.168.0.110:8503"/>
-    <hyperlink ref="E17" r:id="rId3" display="https://auditincentivecal.streamlit.app/"/>
+    <hyperlink ref="E19" r:id="rId3" display="https://auditincentivecal.streamlit.app/"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/ONLINE2.xlsx
+++ b/ONLINE2.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="42">
   <si>
     <t>S.NO</t>
   </si>
@@ -123,6 +123,9 @@
   </si>
   <si>
     <t>PDF TO EXCEL</t>
+  </si>
+  <si>
+    <t>https://auditpdftoexcel.streamlit.app/</t>
   </si>
   <si>
     <t>PPT PREPARATION</t>
@@ -774,7 +777,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -790,6 +793,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="6" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="6"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1153,7 +1157,7 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="3">
-        <f t="shared" ref="A3:A24" si="0">ROW()-1</f>
+        <f t="shared" ref="A3:A26" si="0">ROW()-1</f>
         <v>2</v>
       </c>
       <c r="B3" s="4" t="s">
@@ -1369,7 +1373,7 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="0"/>
         <v>16</v>
       </c>
       <c r="B17" s="4" t="s">
@@ -1381,10 +1385,13 @@
       <c r="D17" t="s">
         <v>30</v>
       </c>
+      <c r="E17" s="9" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="0"/>
         <v>17</v>
       </c>
       <c r="B18" s="4" t="s">
@@ -1394,84 +1401,84 @@
         <v>29</v>
       </c>
       <c r="D18" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="0"/>
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="0"/>
         <v>19</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C20" s="3"/>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="0"/>
         <v>20</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C21" s="3"/>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="0"/>
         <v>21</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C22" s="3"/>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="0"/>
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="0"/>
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="0"/>
         <v>24</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" si="0"/>
         <v>25</v>
       </c>
     </row>
@@ -1484,6 +1491,7 @@
     <hyperlink ref="L4" r:id="rId2"/>
     <hyperlink ref="E4" r:id="rId2" display="http://192.168.0.110:8503"/>
     <hyperlink ref="E19" r:id="rId3" display="https://auditincentivecal.streamlit.app/"/>
+    <hyperlink ref="E17" r:id="rId4" display="https://auditpdftoexcel.streamlit.app/"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
